--- a/data/file_generation/input/data_205/成交区间.xlsx
+++ b/data/file_generation/input/data_205/成交区间.xlsx
@@ -10772,18 +10772,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5AD2B0C-0632-48B5-9E4A-8B5AA358ADBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E544E57-2FB4-460D-92D8-A4CC23C0FA58}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F867DF9-C702-4180-AD30-BE6CE7B8D020}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407B1DA6-9C9F-4CBB-BECC-613A9FB1F289}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9F46BCA-9640-45B9-AE5E-92EF0DB37C9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC15B7E6-780F-4728-808C-1F102D26CBDC}"/>
 </file>